--- a/data/27September-Gold_Diggers-v-Oaks.xlsx
+++ b/data/27September-Gold_Diggers-v-Oaks.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:N167"/>
   <sheetData>
     <row r="1">
@@ -545,8 +545,10 @@
       <c r="D43" t="s">
         <v>15</v>
       </c>
-      <c r="E43" t="s">
-        <v>16</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UCDCLC</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1308,8 +1310,10 @@
       <c r="D126" t="s">
         <v>15</v>
       </c>
-      <c r="E126" t="s">
-        <v>37</v>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="127">
